--- a/data/tags/סינגלים חדשים זמרים מתחילים/global/2026-04-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/global/2026-04-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>להקת נשמחה - לב לבן קאבר</v>
+        <v>נויה ערבה - לב לבן קאבר</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410320&amp;sid=9ddf9caaab80e46f7790a438dc9f07e9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410357&amp;sid=98dc1c04e8e9667665107f61648b9751</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>להקת נשמחה - לב לבן קאבר</v>
+        <v>נויה ערבה - לב לבן קאבר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>חביב חיים בן אריה - יוצא לאור קאבר</v>
+        <v>מתן חבקוק - והיא שעמדה קאבר</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410319&amp;sid=9ddf9caaab80e46f7790a438dc9f07e9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410356&amp;sid=98dc1c04e8e9667665107f61648b9751</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>חביב חיים בן אריה - יוצא לאור קאבר</v>
+        <v>מתן חבקוק - והיא שעמדה קאבר</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>אריאל עדן - הוויה קאבר</v>
+        <v>דניאל שם-טוב - מה אני רוצה באמת קאבר</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410318&amp;sid=9ddf9caaab80e46f7790a438dc9f07e9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410353&amp;sid=98dc1c04e8e9667665107f61648b9751</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,126 +545,12 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>אריאל עדן - הוויה קאבר</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>אליאור נונה - שבע בערב קאבר</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-04-01</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410317&amp;sid=9ddf9caaab80e46f7790a438dc9f07e9</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-04-01</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>אליאור נונה - שבע בערב קאבר</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>אדיר ניזרי - דקלון ובית''ר - גרסת האוהדים</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-04-01</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410316&amp;sid=9ddf9caaab80e46f7790a438dc9f07e9</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-04-01</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>אדיר ניזרי - דקלון ובית''ר - גרסת האוהדים</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>אברהם דהאן - בשורות טובות קאבר</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-04-01</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410315&amp;sid=9ddf9caaab80e46f7790a438dc9f07e9</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-04-01</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>אברהם דהאן - בשורות טובות קאבר</v>
+        <v>דניאל שם-טוב - מה אני רוצה באמת קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/global/2026-04-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/global/2026-04-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>נויה ערבה - לב לבן קאבר</v>
+        <v>חגית ביטון חג'בי - תפילות קאבר</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-04</v>
+        <v>2026-04-06</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410357&amp;sid=98dc1c04e8e9667665107f61648b9751</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410382&amp;sid=d001edcec81b3dfe9262a7ef1c4df041</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-04</v>
+        <v>2026-04-06</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>נויה ערבה - לב לבן קאבר</v>
+        <v>חגית ביטון חג'בי - תפילות קאבר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>מתן חבקוק - והיא שעמדה קאבר</v>
+        <v>אביחי טהיא - לבחור נכון קאבר</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-04-04</v>
+        <v>2026-04-06</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410356&amp;sid=98dc1c04e8e9667665107f61648b9751</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410377&amp;sid=d001edcec81b3dfe9262a7ef1c4df041</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-04-04</v>
+        <v>2026-04-06</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,50 +507,12 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>מתן חבקוק - והיא שעמדה קאבר</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>דניאל שם-טוב - מה אני רוצה באמת קאבר</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-04-04</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410353&amp;sid=98dc1c04e8e9667665107f61648b9751</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-04-04</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>דניאל שם-טוב - מה אני רוצה באמת קאבר</v>
+        <v>אביחי טהיא - לבחור נכון קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
   </ignoredErrors>
 </worksheet>
 </file>